--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to Device</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to Device</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -923,7 +923,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsDevice</t>
   </si>
   <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1543,7 +1543,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="93.890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.35546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="61.40234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -923,7 +923,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsDevice</t>
   </si>
   <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
+    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1543,7 +1543,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="92.35546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="137.97265625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="61.40234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,10 +920,10 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsDevice</t>
-  </si>
-  <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMeasurementDevice</t>
+  </si>
+  <si>
+    <t>663: terminologyMaps using VF_VitalsMeasurementDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1533,7 +1533,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1543,7 +1543,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="137.97265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="61.40234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsCPMDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
